--- a/docs/test-cases/SPM-39_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-39_Test_Cases.xlsx
@@ -498,6 +498,7 @@
       <c r="E1" s="8" t="n"/>
       <c r="F1" s="9" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -1298,6 +1299,8 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
@@ -1476,6 +1479,7 @@
       </c>
       <c r="F37" s="9" t="n"/>
     </row>
+    <row r="38"/>
     <row r="39" ht="179.5" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
@@ -1507,8 +1511,8 @@
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E35:F35"/>
     <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F35"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="B37:D37"/>
@@ -1664,6 +1668,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -1828,6 +1833,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -1994,6 +2000,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -2157,6 +2164,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -2319,6 +2327,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -2483,6 +2492,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -2647,6 +2657,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -2813,6 +2824,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -2979,6 +2991,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -3075,7 +3088,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded — no flag can be cleared from the app, so reload the demo data before this test.
-One-North Seminar Room (ONE-SEM) seats 80 theatre-style and has one approved future booking: 'Tanjong Legal CPD Seminar' on 28 Oct 2026, whose event expects 70 people. Its coordinator is Joel Fernandez.
+One-North Seminar Room (ONE-SEM) seats 80 theatre-style and has one approved future booking: 'Tanjong Legal CPD Seminar' on 3 Nov 2026, whose event expects 70 people. Its coordinator is Joel Fernandez.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
@@ -3143,6 +3156,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -3396,7 +3410,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-One-North Auditorium (ONE-AUD) seats 180 theatre-style and has one approved future booking: 'Bayu Energy Transition Panel' on 3 Nov 2026, whose event expects 160 people.
+One-North Auditorium (ONE-AUD) seats 180 theatre-style and has one approved future booking: 'Bayu Energy Transition Panel' on 9 Nov 2026, whose event expects 160 people.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
@@ -3462,6 +3476,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -3623,6 +3638,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -3719,7 +3735,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-Changi Conference Centre (CBP-CONF) has one APPROVED future booking, 'Anchorpoint Supply Chain Briefing' on 20 Oct 2026, and one PENDING future booking, 'Pearl Delta Safety Conference'.
+Changi Conference Centre (CBP-CONF) has one APPROVED future booking, 'Anchorpoint Supply Chain Briefing' on 26 Oct 2026, and one PENDING future booking, 'Pearl Delta Safety Conference'.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
@@ -3788,6 +3804,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -3884,7 +3901,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-Jurong Training Room (JUR-TRN) has one approved FUTURE booking, 'Harbourline Claims Systems Training' on 13 Oct 2026, and one approved PAST booking, 'Meridian Compliance Training' from 25 Aug 2026.
+Jurong Training Room (JUR-TRN) has one approved FUTURE booking, 'Harbourline Claims Systems Training' on 19 Oct 2026, and one approved PAST booking, 'Meridian Compliance Training' from 31 Aug 2026.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
@@ -3952,6 +3969,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -4119,6 +4137,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -4215,7 +4234,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-Jurong Expo Floor (JUR-EXP) has one approved future booking, 'Sundara Hospitality Trade Showcase' on 24 Nov 2026, whose event requires Loading bay access as a mandatory facility. Its coordinator is Daniel Tan.
+Jurong Expo Floor (JUR-EXP) has one approved future booking, 'Sundara Hospitality Trade Showcase' on 30 Nov 2026, whose event requires Loading bay access as a mandatory facility. Its coordinator is Daniel Tan.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
@@ -4282,6 +4301,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -4444,6 +4464,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -4609,6 +4630,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -4774,6 +4796,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -4939,6 +4962,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -5101,6 +5125,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -5272,6 +5297,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -5438,6 +5464,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -5604,6 +5631,7 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>

--- a/docs/test-cases/SPM-39_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-39_Test_Cases.xlsx
@@ -158,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -218,6 +218,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -510,12 +513,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="24">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="27" t="inlineStr">
         <is>
           <t>SPM-39: As Venue Staff, I want to maintain venue information so that Event Coordinators can identify venues that meet event requirements</t>
         </is>
@@ -527,32 +530,32 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="27" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -579,27 +582,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC01</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>Venue Staff can create a venue record</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -618,27 +621,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC02</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Empty venue form is rejected with a message on every required field</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -657,27 +660,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC03</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>A venue code that is already in use is rejected</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -696,27 +699,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC04</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>A Coordinator cannot reach the Add venue form</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>AC1, AC5</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -735,38 +738,42 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC05</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>Location, capacity, facilities and accessibility are all recorded and persist</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G8" s="28" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H8" s="28" t="n"/>
-      <c r="I8" s="28" t="n"/>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Week 7 #1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -774,27 +781,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC06</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>A maximum capacity of zero is rejected</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -813,27 +820,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC07</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>Several layouts are recorded, each with its own capacity</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -852,27 +859,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC08</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>A layout row with no capacity is rejected</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -891,27 +898,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC09</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>The same layout cannot be recorded twice</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -930,27 +937,27 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC10</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>Opening hours and turnaround times are recorded</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -969,27 +976,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC11</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>A closing time before the opening time is rejected</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1008,27 +1015,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC12</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>A negative setup time is rejected</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1047,38 +1054,42 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC13</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>Venue Staff can update an existing venue</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G16" s="28" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H16" s="28" t="n"/>
-      <c r="I16" s="28" t="n"/>
+      <c r="I16" s="28" t="inlineStr">
+        <is>
+          <t>Week 7 #1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -1086,27 +1097,27 @@
           <t>TC14</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC14</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>A Coordinator cannot update a venue</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1125,27 +1136,27 @@
           <t>TC15</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC15</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>A retired venue is no longer offered to a Coordinator</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1164,27 +1175,27 @@
           <t>TC16</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC16</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>Venue Staff can find a retired venue and restore it</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="28" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1203,27 +1214,27 @@
           <t>TC17</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC17</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>Reducing a layout below an approved booking's attendance flags that booking</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1242,38 +1253,42 @@
           <t>TC18</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC18</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>A layout capacity exactly equal to the expected attendance does not flag</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G21" s="28" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H21" s="28" t="n"/>
-      <c r="I21" s="28" t="n"/>
+      <c r="I21" s="28" t="inlineStr">
+        <is>
+          <t>Week 7 #1</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="24">
       <c r="A22" s="9" t="inlineStr">
@@ -1281,27 +1296,27 @@
           <t>TC19</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC19</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>One seat below the expected attendance does flag</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1320,27 +1335,27 @@
           <t>TC20</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC20</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>Retiring a venue flags approved bookings but not pending ones</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="28" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="28" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1359,27 +1374,27 @@
           <t>TC21</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC21</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>Retiring a venue does not flag bookings that have already finished</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1398,38 +1413,42 @@
           <t>TC22</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC22</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>Changing details that cannot affect suitability flags nothing</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="28" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F25" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G25" s="28" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H25" s="28" t="n"/>
-      <c r="I25" s="28" t="n"/>
+      <c r="I25" s="28" t="inlineStr">
+        <is>
+          <t>Week 7 #1</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="24">
       <c r="A26" s="9" t="inlineStr">
@@ -1437,27 +1456,27 @@
           <t>TC23</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC23</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>Removing a facility an event requires flags its booking</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="28" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F26" s="28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1476,55 +1495,59 @@
           <t>TC24</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC24</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t>Removing a facility no event requires flags nothing</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="28" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="28" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F27" s="28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
       <c r="G27" s="28" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H27" s="28" t="n"/>
-      <c r="I27" s="28" t="n"/>
+      <c r="I27" s="28" t="inlineStr">
+        <is>
+          <t>Week 7 #1</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="24"/>
     <row r="29" ht="15.75" customHeight="1" s="24"/>
     <row r="30" ht="15.75" customHeight="1" s="24">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C30" s="25" t="n"/>
       <c r="D30" s="26" t="n"/>
-      <c r="E30" s="1" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1532,19 +1555,19 @@
       <c r="F30" s="26" t="n"/>
     </row>
     <row r="31" ht="57.75" customHeight="1" s="24">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>Venue Staff can create a venue record.</t>
         </is>
       </c>
       <c r="C31" s="25" t="n"/>
       <c r="D31" s="26" t="n"/>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC01
 SPM-39-TC02
@@ -1555,19 +1578,19 @@
       <c r="F31" s="26" t="n"/>
     </row>
     <row r="32" ht="30.75" customHeight="1" s="24">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>Venue information includes location, capacity, facilities and accessibility information.</t>
         </is>
       </c>
       <c r="C32" s="25" t="n"/>
       <c r="D32" s="26" t="n"/>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC05
 SPM-39-TC06</t>
@@ -1576,19 +1599,19 @@
       <c r="F32" s="26" t="n"/>
     </row>
     <row r="33" ht="44.25" customHeight="1" s="24">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>Supported room layouts can be recorded, each with its own capacity value.</t>
         </is>
       </c>
       <c r="C33" s="25" t="n"/>
       <c r="D33" s="26" t="n"/>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E33" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC07
 SPM-39-TC08
@@ -1598,19 +1621,19 @@
       <c r="F33" s="26" t="n"/>
     </row>
     <row r="34" ht="44.25" customHeight="1" s="24">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>Venue operating information can be recorded.</t>
         </is>
       </c>
       <c r="C34" s="25" t="n"/>
       <c r="D34" s="26" t="n"/>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E34" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC10
 SPM-39-TC11
@@ -1620,19 +1643,19 @@
       <c r="F34" s="26" t="n"/>
     </row>
     <row r="35" ht="44.25" customHeight="1" s="24">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>Authorised users can update venue information.</t>
         </is>
       </c>
       <c r="C35" s="25" t="n"/>
       <c r="D35" s="26" t="n"/>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC04
 SPM-39-TC13
@@ -1642,19 +1665,19 @@
       <c r="F35" s="26" t="n"/>
     </row>
     <row r="36" ht="30.75" customHeight="1" s="24">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr">
         <is>
           <t>Unavailable or inactive venues are not presented as available options.</t>
         </is>
       </c>
       <c r="C36" s="25" t="n"/>
       <c r="D36" s="26" t="n"/>
-      <c r="E36" s="23" t="inlineStr">
+      <c r="E36" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC15
 SPM-39-TC16</t>
@@ -1663,19 +1686,19 @@
       <c r="F36" s="26" t="n"/>
     </row>
     <row r="37" ht="111.75" customHeight="1" s="24">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="B37" s="23" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>When a venue's attributes are updated or it is retired, existing bookings that may be affected are flagged for review rather than automatically changed, and the assigned Coordinator is notified.</t>
         </is>
       </c>
       <c r="C37" s="25" t="n"/>
       <c r="D37" s="26" t="n"/>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E37" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC17
 SPM-39-TC18
@@ -1691,12 +1714,12 @@
     </row>
     <row r="38" ht="15.75" customHeight="1" s="24"/>
     <row r="39" ht="179.25" customHeight="1" s="24">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="27" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B39" s="28" t="inlineStr">
         <is>
           <t>prisma/schema.prisma
 prisma/migrations/20260919165337_add_venue_booking_review_flag/migration.sql
@@ -2759,7 +2782,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC08</t>
         </is>
@@ -2771,7 +2794,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Venue 'Test Meeting Room' (TEST-01) exists.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
@@ -2784,7 +2807,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Open 'Test Meeting Room' from the Venues list
 2. Click 'Add a layout'
@@ -2799,7 +2822,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Layout: Theatre
 Seats: (left empty)</t>
@@ -2812,7 +2835,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>A message 'Every layout needs a capacity of at least 1.' appears above the layout rows.
 The change is not saved — reopening the venue does not show a Theatre layout.</t>
@@ -2825,7 +2848,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -2857,7 +2880,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>A message 'Every layout needs a capacity of at least 1.' appears above the layout rows.
 The change is not saved — reopening the venue does not show a Theatre layout.</t>
@@ -2925,7 +2948,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>A message 'Every layout needs a capacity of at least 1.' appears above the layout rows.
 The change is not saved — reopening the venue does not show a Theatre layout.</t>
@@ -3990,7 +4013,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC09</t>
         </is>
@@ -4002,7 +4025,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Venue 'Test Meeting Room' (TEST-01) exists.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
@@ -4015,7 +4038,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Open 'Test Meeting Room' from the Venues list
 2. Click 'Add a layout' and choose Classroom
@@ -4031,7 +4054,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>First layout: Classroom
 All seven layouts: Theatre, Classroom, Boardroom, Banquet, Exhibition, U-shape, Cabaret</t>
@@ -4044,7 +4067,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Classroom is not offered in the second row's layout list — only the layouts not already used are offered.
 Once all seven layouts are listed, the 'Add a layout' button is disabled and 'Every layout is already listed.' is shown beneath it.</t>
@@ -4057,7 +4080,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -4089,7 +4112,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Classroom is not offered in the second row's layout list — only the layouts not already used are offered.
 Once all seven layouts are listed, the 'Add a layout' button is disabled and 'Every layout is already listed.' is shown beneath it.</t>
@@ -4157,7 +4180,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Classroom is not offered in the second row's layout list — only the layouts not already used are offered.
 Once all seven layouts are listed, the 'Add a layout' button is disabled and 'Every layout is already listed.' is shown beneath it.</t>
@@ -5222,7 +5245,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC10</t>
         </is>
@@ -5234,7 +5257,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Venue 'Test Meeting Room' (TEST-01) exists.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
@@ -5247,7 +5270,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Open 'Test Meeting Room' from the Venues list
 2. Set 'Opens at' and 'Closes at'
@@ -5263,7 +5286,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Opens at: 07:00 am
 Closes at: 11:00 pm
@@ -5278,7 +5301,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>On reopening, Opens at shows 07:00, Closes at 23:00, Setup minutes 45 and Teardown minutes 30.
 The Venues list shows Hours as '07:00–23:00' for this venue.</t>
@@ -5291,7 +5314,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -5323,7 +5346,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>On reopening, Opens at shows 07:00, Closes at 23:00, Setup minutes 45 and Teardown minutes 30.
 The Venues list shows Hours as '07:00–23:00' for this venue.</t>
@@ -5391,7 +5414,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>On reopening, Opens at shows 07:00, Closes at 23:00, Setup minutes 45 and Teardown minutes 30.
 The Venues list shows Hours as '07:00–23:00' for this venue.</t>
@@ -6456,7 +6479,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC11</t>
         </is>
@@ -6468,7 +6491,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Venue 'Test Meeting Room' (TEST-01) exists.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
@@ -6481,7 +6504,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Open 'Test Meeting Room' from the Venues list
 2. Set 'Opens at' to the later time
@@ -6496,7 +6519,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Opens at: 06:00 pm
 Closes at: 09:00 am</t>
@@ -6509,7 +6532,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Under 'Closes at': 'Closing time must be after opening time.'
 The change is not saved — reopening the venue shows the previous hours.</t>
@@ -6522,7 +6545,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -6554,7 +6577,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Under 'Closes at': 'Closing time must be after opening time.'
 The change is not saved — reopening the venue shows the previous hours.</t>
@@ -6622,7 +6645,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Under 'Closes at': 'Closing time must be after opening time.'
 The change is not saved — reopening the venue shows the previous hours.</t>
@@ -7687,7 +7710,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC12</t>
         </is>
@@ -7699,7 +7722,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Venue 'Test Meeting Room' (TEST-01) exists.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
@@ -7712,7 +7735,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Open 'Test Meeting Room' from the Venues list
 2. Type the negative value into 'Setup minutes'
@@ -7726,7 +7749,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Setup minutes: -5</t>
         </is>
@@ -7738,7 +7761,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Under 'Setup minutes': 'Enter a whole number of minutes, 0 or more.'
 The change is not saved.
@@ -7752,7 +7775,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -7784,7 +7807,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Under 'Setup minutes': 'Enter a whole number of minutes, 0 or more.'
 The change is not saved.
@@ -7853,7 +7876,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Under 'Setup minutes': 'Enter a whole number of minutes, 0 or more.'
 The change is not saved.
@@ -8897,7 +8920,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="24" min="1" max="1"/>
@@ -8905,46 +8928,53 @@
     <col width="12.63" customWidth="1" style="24" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="24">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="24">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): After a save that flags no booking, the venue page now reads 'No bookings were affected, so nobody needed to be notified.' instead of 'No approved bookings were affected, so nobody needed to be notified.' (SPM-80, Week 7 Change #1: changing a venue's setup or turnaround time now re-checks pending requests as well as approved bookings). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="24">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" s="24">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC13</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="44.25" customHeight="1" s="24">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="4" ht="44.25" customHeight="1" s="24">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Demo data loaded.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="71.25" customHeight="1" s="24">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="5" ht="71.25" customHeight="1" s="24">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar
 2. Click the 'Orchard Studio' row
@@ -8954,25 +8984,25 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30.75" customHeight="1" s="24">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="6" ht="30.75" customHeight="1" s="24">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Description: Workshop room with benches, heavy power supply and a new sink</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="71.25" customHeight="1" s="24">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="7" ht="71.25" customHeight="1" s="24">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>A green message 'Changes saved — No approved bookings were affected. No approved bookings were affected, so nobody needed to be notified.' appears at the top of the page.
 The page stays on the venue rather than navigating away.
@@ -8980,45 +9010,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="24">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8" ht="17.25" customHeight="1" s="24">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="24">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9" ht="15.75" customHeight="1" s="24">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B9" s="10" t="n">
         <v>46285</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="24"/>
-    <row r="10" ht="15.75" customHeight="1" s="24">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="24"/>
+    <row r="11" ht="15.75" customHeight="1" s="24">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="24">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="24">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>A green message 'Changes saved — No approved bookings were affected. No approved bookings were affected, so nobody needed to be notified.' appears at the top of the page.
 The page stays on the venue rather than navigating away.
@@ -9026,68 +9056,68 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="24">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="24">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="24">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Kayal</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="24">
       <c r="A15" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Kayal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="24">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B16" s="16" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="24"/>
-    <row r="17" ht="15.75" customHeight="1" s="24">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="24"/>
+    <row r="18" ht="15.75" customHeight="1" s="24">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="24">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="B18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="24">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>A green message 'Changes saved — No approved bookings were affected. No approved bookings were affected, so nobody needed to be notified.' appears at the top of the page.
 The page stays on the venue rather than navigating away.
@@ -9095,53 +9125,52 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="24">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="24">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="24">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="24">
       <c r="A22" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="24">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B23" s="21" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="24"/>
     <row r="24" ht="15.75" customHeight="1" s="24"/>
     <row r="25" ht="15.75" customHeight="1" s="24"/>
     <row r="26" ht="15.75" customHeight="1" s="24"/>
@@ -10120,6 +10149,9 @@
     <row r="999" ht="15.75" customHeight="1" s="24"/>
     <row r="1000" ht="15.75" customHeight="1" s="24"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -10153,7 +10185,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC14</t>
         </is>
@@ -10165,7 +10197,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Demo data loaded.
 Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
@@ -10178,7 +10210,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar
 2. Click on a venue row
@@ -10193,7 +10225,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Account: daniel.tan@connectsphere.com (Event Coordinator)
 Venue: Marina Grand Hall</t>
@@ -10206,7 +10238,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Clicking a row does nothing — rows are not links for this role, and no Status column is shown.
 The edit page shows 'Only Venue Staff can change a venue' and a 'Back to Venues' button.
@@ -10220,7 +10252,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -10252,7 +10284,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Clicking a row does nothing — rows are not links for this role, and no Status column is shown.
 The edit page shows 'Only Venue Staff can change a venue' and a 'Back to Venues' button.
@@ -10321,7 +10353,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Clicking a row does nothing — rows are not links for this role, and no Status column is shown.
 The edit page shows 'Only Venue Staff can change a venue' and a 'Back to Venues' button.
@@ -11387,7 +11419,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC15</t>
         </is>
@@ -11399,7 +11431,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Venue 'Test Meeting Room' (TEST-01) exists, is active and has no bookings.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
@@ -11412,7 +11444,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Open 'Test Meeting Room' from the Venues list
 2. Click 'Retire venue'
@@ -11430,7 +11462,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Reason: Closed for renovation until March</t>
         </is>
@@ -11442,7 +11474,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>For Venue Staff the venue page gains a 'Retired' label, an amber 'This venue is retired' panel, and the button changes to 'Restore venue'.
 For the Coordinator, 'Test Meeting Room' does not appear in the Venues list at all.
@@ -11456,7 +11488,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -11488,7 +11520,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>For Venue Staff the venue page gains a 'Retired' label, an amber 'This venue is retired' panel, and the button changes to 'Restore venue'.
 For the Coordinator, 'Test Meeting Room' does not appear in the Venues list at all.
@@ -11557,7 +11589,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>For Venue Staff the venue page gains a 'Retired' label, an amber 'This venue is retired' panel, and the button changes to 'Restore venue'.
 For the Coordinator, 'Test Meeting Room' does not appear in the Venues list at all.
@@ -12623,7 +12655,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC16</t>
         </is>
@@ -12635,7 +12667,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Venue 'Test Meeting Room' (TEST-01) has been retired in TC15.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
@@ -12648,7 +12680,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar
 2. Set the 'Show' filter to 'Retired only'
@@ -12665,7 +12697,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Venue: Test Meeting Room (TEST-01)
 Show filter: Retired only, then Active only</t>
@@ -12678,7 +12710,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>With 'Retired only' selected, 'Test Meeting Room' is listed with Status 'Retired' in amber.
 After Restore, a green 'Venue restored' message appears, the 'Retired' label and amber panel disappear, and the button changes back to 'Retire venue'.
@@ -12692,7 +12724,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -12724,7 +12756,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>With 'Retired only' selected, 'Test Meeting Room' is listed with Status 'Retired' in amber.
 After Restore, a green 'Venue restored' message appears, the 'Retired' label and amber panel disappear, and the button changes back to 'Retire venue'.
@@ -12793,7 +12825,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>With 'Retired only' selected, 'Test Meeting Room' is listed with Status 'Retired' in amber.
 After Restore, a green 'Venue restored' message appears, the 'Retired' label and amber panel disappear, and the button changes back to 'Retire venue'.
@@ -13859,7 +13891,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC17</t>
         </is>
@@ -13871,7 +13903,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Demo data freshly loaded — no flag can be cleared from the app, so reload the demo data before this test.
 One-North Seminar Room (ONE-SEM) seats 80 theatre-style and has one approved future booking: 'Tanjong Legal CPD Seminar' on 28 Oct 2026, whose event expects 70 people. Its coordinator is Joel Fernandez.
@@ -13885,7 +13917,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Open 'One-North Seminar Room' from the Venues list
 2. Change the Theatre layout's Seats value
@@ -13899,7 +13931,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Theatre seats: change 80 to 60 (the event expects 70)</t>
         </is>
@@ -13911,7 +13943,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>An amber panel appears at the top: 'Changes saved — 1 booking flagged for review, coordinators notified'.
 It states the bookings have NOT been changed and that each is flagged for its coordinator to decide what to do.
@@ -13926,7 +13958,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -13958,7 +13990,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>An amber panel appears at the top: 'Changes saved — 1 booking flagged for review, coordinators notified'.
 It states the bookings have NOT been changed and that each is flagged for its coordinator to decide what to do.
@@ -14028,7 +14060,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>An amber panel appears at the top: 'Changes saved — 1 booking flagged for review, coordinators notified'.
 It states the bookings have NOT been changed and that each is flagged for its coordinator to decide what to do.
@@ -15083,142 +15115,142 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="27" t="inlineStr">
         <is>
           <t>Question / ambiguity for the PO or developer</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="27" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="2" ht="84.75" customHeight="1" s="24">
-      <c r="A2" s="23" t="n">
+      <c r="A2" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>AC7 says the assigned Coordinator is notified, but there is no notifications screen in the application. The top-bar bell and every sidebar 'Notifications' link point at a page that does not exist yet, so a tester can see the confirmation that coordinators were notified but cannot open a coordinator's inbox to verify it. Is building that screen part of SPM-39, or a separate story?</t>
         </is>
       </c>
-      <c r="C2" s="23" t="n"/>
+      <c r="C2" s="28" t="n"/>
     </row>
     <row r="3" ht="71.25" customHeight="1" s="24">
-      <c r="A3" s="23" t="n">
+      <c r="A3" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>AC7 says affected bookings are 'flagged for review', but nothing in the application shows the flag once the save confirmation has gone. There is no review queue and no flag indicator on any booking screen, so the flag is only visible in the database. How should a tester verify that a flag persists?</t>
         </is>
       </c>
-      <c r="C3" s="23" t="n"/>
+      <c r="C3" s="28" t="n"/>
     </row>
     <row r="4" ht="57.75" customHeight="1" s="24">
-      <c r="A4" s="23" t="n">
+      <c r="A4" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Nothing can clear a flag once set — that was scoped out as a follow-up story. Every AC7 test therefore leaves permanent state, so the demo data has to be reloaded between runs. Is that acceptable for the test cycle, or should the acknowledge/resolve story be pulled into SPM-39?</t>
         </is>
       </c>
-      <c r="C4" s="23" t="n"/>
+      <c r="C4" s="28" t="n"/>
     </row>
     <row r="5" ht="71.25" customHeight="1" s="24">
-      <c r="A5" s="23" t="n">
+      <c r="A5" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>AC7 says 'existing bookings that may be affected'. The implementation treats only approved bookings that have not yet finished as candidates: pending, rejected, cancelled and already-finished bookings are never flagged. TC20 and TC21 test it this way — please confirm it matches the intent of discussion #120 and #122.</t>
         </is>
       </c>
-      <c r="C5" s="23" t="n"/>
+      <c r="C5" s="28" t="n"/>
     </row>
     <row r="6" ht="71.25" customHeight="1" s="24">
-      <c r="A6" s="23" t="n">
+      <c r="A6" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>AC7 also says bookings are not 'automatically changed'. A tester cannot confirm this independently, because no screen shows a booking's venue, layout, times or status — the Booking Requests screen is not built. Currently the only evidence is the wording of the confirmation panel. Is that enough, or should verification wait for the bookings screen?</t>
         </is>
       </c>
-      <c r="C6" s="23" t="n"/>
+      <c r="C6" s="28" t="n"/>
     </row>
     <row r="7" ht="84.75" customHeight="1" s="24">
-      <c r="A7" s="23" t="n">
+      <c r="A7" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>AC6 covers both 'unavailable' and 'inactive' venues, but only the inactive half is testable. Retired venues are excluded from the Coordinator's catalogue (TC15). The venue search and booking request screens that would 'present available options' are not built, and venue unavailability (maintenance blocks) has no screen either, so the 'unavailable' half cannot be exercised. Is AC6 considered satisfied for this story?</t>
         </is>
       </c>
-      <c r="C7" s="23" t="n"/>
+      <c r="C7" s="28" t="n"/>
     </row>
     <row r="8" ht="57.75" customHeight="1" s="24">
-      <c r="A8" s="23" t="n">
+      <c r="A8" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>A layout's capacity is allowed to exceed the venue's maximum capacity, and the demo data relies on it — Jurong Training Room has a Theatre layout of 70 against a maximum capacity of 60. Intended, or should the form reject a layout larger than the room?</t>
         </is>
       </c>
-      <c r="C8" s="23" t="n"/>
+      <c r="C8" s="28" t="n"/>
     </row>
     <row r="9" ht="44.25" customHeight="1" s="24">
-      <c r="A9" s="23" t="n">
+      <c r="A9" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>The rule that a closing time must be after the opening time is only enforced in the browser (TC11). The API itself accepts a venue that closes before it opens. Should the server reject it too?</t>
         </is>
       </c>
-      <c r="C9" s="23" t="n"/>
+      <c r="C9" s="28" t="n"/>
     </row>
     <row r="10" ht="84.75" customHeight="1" s="24">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Narrowing a venue's opening hours is deliberately not treated as an impact yet, so a booking that now falls outside the opening hours is NOT flagged. This was deferred because comparing the stored opening time text against a booking's date and time needs a timezone convention the codebase has not settled. Please confirm this is acceptable for SPM-39 rather than a gap in AC7.</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n"/>
+      <c r="C10" s="28" t="n"/>
     </row>
     <row r="11" ht="44.25" customHeight="1" s="24">
-      <c r="A11" s="23" t="n">
+      <c r="A11" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>AC2 mentions 'accessibility information'. This is implemented as accessibility tick boxes only; unlike an event, a venue has no free-text accessibility notes field. Is the tick list sufficient?</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n"/>
+      <c r="C11" s="28" t="n"/>
     </row>
     <row r="12" ht="57.75" customHeight="1" s="24">
-      <c r="A12" s="23" t="n">
+      <c r="A12" s="28" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Duplicate layout names are rejected by the server, but the layout picker only ever offers layouts that are not already used, so the rejection cannot be reached from the interface. TC09 tests the picker instead. No test covers the server-side rule.</t>
         </is>
       </c>
-      <c r="C12" s="23" t="n"/>
+      <c r="C12" s="28" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="24"/>
     <row r="22" ht="15.75" customHeight="1" s="24"/>
@@ -16212,7 +16244,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="24" min="1" max="1"/>
@@ -16220,33 +16252,40 @@
     <col width="12.63" customWidth="1" style="24" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="24">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="24">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): After a save that flags no booking, the venue page now reads 'No bookings were affected, so nobody needed to be notified.' instead of 'No approved bookings were affected, so nobody needed to be notified.' (SPM-80, Week 7 Change #1: changing a venue's setup or turnaround time now re-checks pending requests as well as approved bookings). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="24">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" s="24">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC18</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="84.75" customHeight="1" s="24">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="4" ht="84.75" customHeight="1" s="24">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
 One-North Auditorium (ONE-AUD) seats 180 theatre-style and has one approved future booking: 'Bayu Energy Transition Panel' on 3 Nov 2026, whose event expects 160 people.
@@ -16254,13 +16293,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="44.25" customHeight="1" s="24">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="5" ht="44.25" customHeight="1" s="24">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>1. Open 'One-North Auditorium' from the Venues list
 2. Change the Theatre layout's Seats value
@@ -16268,191 +16307,190 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30.75" customHeight="1" s="24">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="6" ht="30.75" customHeight="1" s="24">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Theatre seats: change 180 to 160 (the event expects exactly 160)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="57.75" customHeight="1" s="24">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="7" ht="57.75" customHeight="1" s="24">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>A green panel appears: 'Changes saved — No approved bookings were affected.'
 No booking is listed as flagged — a room that seats exactly the expected attendance still fits.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="24">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8" ht="17.25" customHeight="1" s="24">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="24">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9" ht="15.75" customHeight="1" s="24">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B9" s="10" t="n">
         <v>46285</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="24"/>
-    <row r="10" ht="15.75" customHeight="1" s="24">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="24"/>
+    <row r="11" ht="15.75" customHeight="1" s="24">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="24">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="24">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>A green panel appears: 'Changes saved — No approved bookings were affected.'
 No booking is listed as flagged — a room that seats exactly the expected attendance still fits.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="24">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="24">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="24">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Kayal</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="24">
       <c r="A15" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Kayal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="24">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B16" s="16" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="24"/>
-    <row r="17" ht="15.75" customHeight="1" s="24">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="24"/>
+    <row r="18" ht="15.75" customHeight="1" s="24">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="24">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="B18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="24">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>A green panel appears: 'Changes saved — No approved bookings were affected.'
 No booking is listed as flagged — a room that seats exactly the expected attendance still fits.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="24">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="24">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="24">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="24">
       <c r="A22" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="24">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B23" s="21" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="24"/>
     <row r="24" ht="15.75" customHeight="1" s="24"/>
     <row r="25" ht="15.75" customHeight="1" s="24"/>
     <row r="26" ht="15.75" customHeight="1" s="24"/>
@@ -17431,6 +17469,9 @@
     <row r="999" ht="15.75" customHeight="1" s="24"/>
     <row r="1000" ht="15.75" customHeight="1" s="24"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -17464,7 +17505,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC19</t>
         </is>
@@ -17476,7 +17517,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Run immediately after TC18, with One-North Auditorium's Theatre layout at 160 seats and 'Bayu Energy Transition Panel' still unflagged.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
@@ -17489,7 +17530,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Open 'One-North Auditorium' from the Venues list
 2. Change the Theatre layout's Seats value
@@ -17503,7 +17544,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Theatre seats: change 160 to 159 (the event expects 160)</t>
         </is>
@@ -17515,7 +17556,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>An amber panel appears: 'Changes saved — 1 booking flagged for review, coordinators notified'.
 It lists 'Bayu Energy Transition Panel: the booked layout no longer seats the expected attendance'.</t>
@@ -17528,7 +17569,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -17560,7 +17601,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>An amber panel appears: 'Changes saved — 1 booking flagged for review, coordinators notified'.
 It lists 'Bayu Energy Transition Panel: the booked layout no longer seats the expected attendance'.</t>
@@ -17628,7 +17669,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>An amber panel appears: 'Changes saved — 1 booking flagged for review, coordinators notified'.
 It lists 'Bayu Energy Transition Panel: the booked layout no longer seats the expected attendance'.</t>
@@ -18693,7 +18734,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC20</t>
         </is>
@@ -18705,7 +18746,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
 Changi Conference Centre (CBP-CONF) has one APPROVED future booking, 'Anchorpoint Supply Chain Briefing' on 20 Oct 2026, and one PENDING future booking, 'Pearl Delta Safety Conference'.
@@ -18719,7 +18760,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Open 'Changi Conference Centre' from the Venues list
 2. Click 'Retire venue'
@@ -18734,7 +18775,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Reason: Air conditioning replacement, closed indefinitely</t>
         </is>
@@ -18746,7 +18787,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>The confirmation dialog states the room will stop appearing in the catalogue, that past bookings are kept, and that any approved future booking will be flagged and its coordinator notified.
 After confirming, an amber panel reads 'Venue retired — 1 booking flagged for review, coordinators notified'.
@@ -18761,7 +18802,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -18793,7 +18834,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>The confirmation dialog states the room will stop appearing in the catalogue, that past bookings are kept, and that any approved future booking will be flagged and its coordinator notified.
 After confirming, an amber panel reads 'Venue retired — 1 booking flagged for review, coordinators notified'.
@@ -18863,7 +18904,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>The confirmation dialog states the room will stop appearing in the catalogue, that past bookings are kept, and that any approved future booking will be flagged and its coordinator notified.
 After confirming, an amber panel reads 'Venue retired — 1 booking flagged for review, coordinators notified'.
@@ -19930,7 +19971,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC21</t>
         </is>
@@ -19942,7 +19983,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
 Jurong Training Room (JUR-TRN) has one approved FUTURE booking, 'Harbourline Claims Systems Training' on 13 Oct 2026, and one approved PAST booking, 'Meridian Compliance Training' from 25 Aug 2026.
@@ -19956,7 +19997,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Open 'Jurong Training Room' from the Venues list
 2. Click 'Retire venue'
@@ -19970,7 +20011,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Venue: Jurong Training Room (JUR-TRN)
 Reason: left blank</t>
@@ -19983,7 +20024,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>An amber panel reads 'Venue retired — 1 booking flagged for review, coordinators notified'.
 Only 'Harbourline Claims Systems Training: the venue has been retired' is listed.
@@ -19997,7 +20038,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -20029,7 +20070,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>An amber panel reads 'Venue retired — 1 booking flagged for review, coordinators notified'.
 Only 'Harbourline Claims Systems Training: the venue has been retired' is listed.
@@ -20098,7 +20139,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>An amber panel reads 'Venue retired — 1 booking flagged for review, coordinators notified'.
 Only 'Harbourline Claims Systems Training: the venue has been retired' is listed.
@@ -21142,7 +21183,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="24" min="1" max="1"/>
@@ -21150,33 +21191,40 @@
     <col width="12.63" customWidth="1" style="24" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="24">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="24">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): After a save that flags no booking, the venue page now reads 'No bookings were affected, so nobody needed to be notified.' instead of 'No approved bookings were affected, so nobody needed to be notified.' (SPM-80, Week 7 Change #1: changing a venue's setup or turnaround time now re-checks pending requests as well as approved bookings). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="24">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" s="24">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC22</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="57.75" customHeight="1" s="24">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="4" ht="57.75" customHeight="1" s="24">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
 Marina Grand Hall (MAR-GH) has two approved future bookings.
@@ -21184,13 +21232,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="57.75" customHeight="1" s="24">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="5" ht="57.75" customHeight="1" s="24">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>1. Open 'Marina Grand Hall' from the Venues list
 2. Change the Description, Floor and Address
@@ -21199,13 +21247,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="57.75" customHeight="1" s="24">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="6" ht="57.75" customHeight="1" s="24">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Description: Flagship hall, refurbished 2026
 Floor: L1 (Main)
@@ -21214,13 +21262,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="71.25" customHeight="1" s="24">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="7" ht="71.25" customHeight="1" s="24">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>A green panel appears: 'Changes saved — No approved bookings were affected.'
 No booking is listed as flagged — renaming, relocating or enlarging a room cannot make it unsuitable.
@@ -21228,45 +21276,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="24">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8" ht="17.25" customHeight="1" s="24">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="24">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9" ht="15.75" customHeight="1" s="24">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B9" s="10" t="n">
         <v>46285</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="24"/>
-    <row r="10" ht="15.75" customHeight="1" s="24">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="24"/>
+    <row r="11" ht="15.75" customHeight="1" s="24">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="24">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="24">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>A green panel appears: 'Changes saved — No approved bookings were affected.'
 No booking is listed as flagged — renaming, relocating or enlarging a room cannot make it unsuitable.
@@ -21274,68 +21322,68 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="24">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="24">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="24">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Kayal</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="24">
       <c r="A15" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Kayal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="24">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B16" s="16" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="24"/>
-    <row r="17" ht="15.75" customHeight="1" s="24">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="24"/>
+    <row r="18" ht="15.75" customHeight="1" s="24">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="24">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="B18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="24">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>A green panel appears: 'Changes saved — No approved bookings were affected.'
 No booking is listed as flagged — renaming, relocating or enlarging a room cannot make it unsuitable.
@@ -21343,53 +21391,52 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="24">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="24">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="24">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="24">
       <c r="A22" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="24">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B23" s="21" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="24"/>
     <row r="24" ht="15.75" customHeight="1" s="24"/>
     <row r="25" ht="15.75" customHeight="1" s="24"/>
     <row r="26" ht="15.75" customHeight="1" s="24"/>
@@ -22368,6 +22415,9 @@
     <row r="999" ht="15.75" customHeight="1" s="24"/>
     <row r="1000" ht="15.75" customHeight="1" s="24"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -22401,7 +22451,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC23</t>
         </is>
@@ -22413,7 +22463,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
 Jurong Expo Floor (JUR-EXP) has one approved future booking, 'Sundara Hospitality Trade Showcase' on 24 Nov 2026, whose event requires Loading bay access as a mandatory facility. Its coordinator is Daniel Tan.
@@ -22427,7 +22477,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Open 'Jurong Expo Floor' from the Venues list
 2. Under 'This venue has', untick 'Loading bay access'
@@ -22441,7 +22491,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Facility to untick: Loading bay access</t>
         </is>
@@ -22453,7 +22503,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>An amber panel reads 'Changes saved — 1 booking flagged for review, coordinators notified'.
 It lists 'Sundara Hospitality Trade Showcase: a facility this event requires is no longer available at this venue'.
@@ -22467,7 +22517,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -22499,7 +22549,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>An amber panel reads 'Changes saved — 1 booking flagged for review, coordinators notified'.
 It lists 'Sundara Hospitality Trade Showcase: a facility this event requires is no longer available at this venue'.
@@ -22568,7 +22618,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>An amber panel reads 'Changes saved — 1 booking flagged for review, coordinators notified'.
 It lists 'Sundara Hospitality Trade Showcase: a facility this event requires is no longer available at this venue'.
@@ -23612,7 +23662,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="24" min="1" max="1"/>
@@ -23620,33 +23670,40 @@
     <col width="12.63" customWidth="1" style="24" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="24">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="24">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): After a save that flags no booking, the venue page now reads 'No bookings were affected, so nobody needed to be notified.' instead of 'No approved bookings were affected, so nobody needed to be notified.' (SPM-80, Week 7 Change #1: changing a venue's setup or turnaround time now re-checks pending requests as well as approved bookings). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="24">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" s="24">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC24</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="84.75" customHeight="1" s="24">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="4" ht="84.75" customHeight="1" s="24">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
 Jurong Expo Floor (JUR-EXP) offers 'Assistance animal friendly', which its approved booking's event does NOT list as a mandatory requirement.
@@ -23654,13 +23711,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="57.75" customHeight="1" s="24">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="5" ht="57.75" customHeight="1" s="24">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>1. Open 'Jurong Expo Floor' from the Venues list
 2. Under 'Accessibility', untick 'Assistance animal friendly'
@@ -23668,191 +23725,190 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1" s="24">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="6" ht="17.25" customHeight="1" s="24">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Facility to untick: Assistance animal friendly</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="57.75" customHeight="1" s="24">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="7" ht="57.75" customHeight="1" s="24">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>A green panel appears: 'Changes saved — No approved bookings were affected.'
 No booking is flagged — a facility the event did not ask for cannot make the room unsuitable for it.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="24">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8" ht="17.25" customHeight="1" s="24">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="24">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9" ht="15.75" customHeight="1" s="24">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B9" s="10" t="n">
         <v>46285</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="24"/>
-    <row r="10" ht="15.75" customHeight="1" s="24">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="24"/>
+    <row r="11" ht="15.75" customHeight="1" s="24">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="24">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="24">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>A green panel appears: 'Changes saved — No approved bookings were affected.'
 No booking is flagged — a facility the event did not ask for cannot make the room unsuitable for it.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="24">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="24">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="24">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Kayal</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="24">
       <c r="A15" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Kayal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="24">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B16" s="16" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="24"/>
-    <row r="17" ht="15.75" customHeight="1" s="24">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="24"/>
+    <row r="18" ht="15.75" customHeight="1" s="24">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="24">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="B18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="24">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>A green panel appears: 'Changes saved — No approved bookings were affected.'
 No booking is flagged — a facility the event did not ask for cannot make the room unsuitable for it.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="24">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="24">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="24">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="24">
       <c r="A22" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="24">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B23" s="21" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="24"/>
     <row r="24" ht="15.75" customHeight="1" s="24"/>
     <row r="25" ht="15.75" customHeight="1" s="24"/>
     <row r="26" ht="15.75" customHeight="1" s="24"/>
@@ -24831,6 +24887,9 @@
     <row r="999" ht="15.75" customHeight="1" s="24"/>
     <row r="1000" ht="15.75" customHeight="1" s="24"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -24864,7 +24923,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC01</t>
         </is>
@@ -24876,7 +24935,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Demo data loaded (16 venues).
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
@@ -24889,7 +24948,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar
 2. Click 'Add venue'
@@ -24904,7 +24963,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Code: TEST-01
 Name: Test Meeting Room
@@ -24919,7 +24978,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>The Venues list reopens and now shows 17 venues.
 'Test Meeting Room' appears with code TEST-01, Location 'Marina Bay', Max capacity 24, Layouts 'None set' in amber, Status 'Active'.</t>
@@ -24932,7 +24991,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -25031,7 +25090,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>The Venues list reopens and now shows 17 venues.
 'Test Meeting Room' appears with code TEST-01, Location 'Marina Bay', Max capacity 24, Layouts 'None set' in amber, Status 'Active'.</t>
@@ -26096,7 +26155,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC02</t>
         </is>
@@ -26108,7 +26167,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
@@ -26120,7 +26179,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar
 2. Click 'Add venue'
@@ -26135,7 +26194,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>All fields left blank</t>
         </is>
@@ -26147,7 +26206,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>The venue is not created and the page does not navigate away.
 Under Code: 'Give the venue a short code, e.g. MAR-GH.'
@@ -26164,7 +26223,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -26196,7 +26255,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>The venue is not created and the page does not navigate away.
 Under Code: 'Give the venue a short code, e.g. MAR-GH.'
@@ -26268,7 +26327,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>The venue is not created and the page does not navigate away.
 Under Code: 'Give the venue a short code, e.g. MAR-GH.'
@@ -27337,7 +27396,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC03</t>
         </is>
@@ -27349,7 +27408,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Demo data loaded — a venue with code MAR-GH (Marina Grand Hall) already exists.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
@@ -27362,7 +27421,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar
 2. Click 'Add venue'
@@ -27377,7 +27436,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Code: MAR-GH
 Name: Duplicate Code Room
@@ -27392,7 +27451,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>A message 'A venue with this code already exists' appears at the top of the form.
 No venue is created — the Venues list still shows the original number of venues.</t>
@@ -27405,7 +27464,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -27437,7 +27496,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>A message 'A venue with this code already exists' appears at the top of the form.
 No venue is created — the Venues list still shows the original number of venues.</t>
@@ -27505,7 +27564,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>A message 'A venue with this code already exists' appears at the top of the form.
 No venue is created — the Venues list still shows the original number of venues.</t>
@@ -28570,7 +28629,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC04</t>
         </is>
@@ -28582,7 +28641,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
         </is>
@@ -28594,7 +28653,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar
 2. Look for an 'Add venue' button in the page header
@@ -28609,7 +28668,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Account: daniel.tan@connectsphere.com (Event Coordinator)</t>
         </is>
@@ -28621,7 +28680,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>No 'Add venue' button is shown on the Venues page.
 The Add venue page shows 'Only Venue Staff can add a venue' with the note that Venue Staff are responsible for venue information, and a 'Back to Venues' button.
@@ -28635,7 +28694,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -28667,7 +28726,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>No 'Add venue' button is shown on the Venues page.
 The Add venue page shows 'Only Venue Staff can add a venue' with the note that Venue Staff are responsible for venue information, and a 'Back to Venues' button.
@@ -28736,7 +28795,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>No 'Add venue' button is shown on the Venues page.
 The Add venue page shows 'Only Venue Staff can add a venue' with the note that Venue Staff are responsible for venue information, and a 'Back to Venues' button.
@@ -29780,7 +29839,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="24" min="1" max="1"/>
@@ -29788,46 +29847,53 @@
     <col width="12.63" customWidth="1" style="24" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="24">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="24">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): After a save that flags no booking, the venue page now reads 'No bookings were affected, so nobody needed to be notified.' instead of 'No approved bookings were affected, so nobody needed to be notified.' (SPM-80, Week 7 Change #1: changing a venue's setup or turnaround time now re-checks pending requests as well as approved bookings). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="24">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" s="24">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC05</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="44.25" customHeight="1" s="24">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="4" ht="44.25" customHeight="1" s="24">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Venue 'Test Meeting Room' (TEST-01) exists from TC01.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="138.75" customHeight="1" s="24">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="5" ht="138.75" customHeight="1" s="24">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar
 2. Click the 'Test Meeting Room' row
@@ -29840,13 +29906,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="71.25" customHeight="1" s="24">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="6" ht="71.25" customHeight="1" s="24">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Floor: L2
 Address: 10 Marina Boulevard
@@ -29856,13 +29922,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="84.75" customHeight="1" s="24">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="7" ht="84.75" customHeight="1" s="24">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>A green message 'Changes saved — No approved bookings were affected.' appears.
 On reopening, Floor shows 'L2', Address '10 Marina Boulevard', Maximum capacity 32, and all four tick boxes are still ticked.
@@ -29870,45 +29936,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="24">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8" ht="17.25" customHeight="1" s="24">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="24">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9" ht="15.75" customHeight="1" s="24">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B9" s="10" t="n">
         <v>46285</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="24"/>
-    <row r="10" ht="15.75" customHeight="1" s="24">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="24"/>
+    <row r="11" ht="15.75" customHeight="1" s="24">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="24">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="24">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>A green message 'Changes saved — No approved bookings were affected.' appears.
 On reopening, Floor shows 'L2', Address '10 Marina Boulevard', Maximum capacity 32, and all four tick boxes are still ticked.
@@ -29916,68 +29982,68 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="24">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="24">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="24">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Kayal</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="24">
       <c r="A15" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Kayal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="24">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B16" s="16" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="24"/>
-    <row r="17" ht="15.75" customHeight="1" s="24">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="24"/>
+    <row r="18" ht="15.75" customHeight="1" s="24">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="24">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="B18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="24">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>A green message 'Changes saved — No approved bookings were affected.' appears.
 On reopening, Floor shows 'L2', Address '10 Marina Boulevard', Maximum capacity 32, and all four tick boxes are still ticked.
@@ -29985,53 +30051,52 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="24">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="24">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="24">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="24">
       <c r="A22" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="24">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B23" s="21" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="24"/>
     <row r="24" ht="15.75" customHeight="1" s="24"/>
     <row r="25" ht="15.75" customHeight="1" s="24"/>
     <row r="26" ht="15.75" customHeight="1" s="24"/>
@@ -31010,6 +31075,9 @@
     <row r="999" ht="15.75" customHeight="1" s="24"/>
     <row r="1000" ht="15.75" customHeight="1" s="24"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -31043,7 +31111,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC06</t>
         </is>
@@ -31055,7 +31123,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
@@ -31067,7 +31135,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar
 2. Click 'Add venue'
@@ -31083,7 +31151,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Code: TEST-02
 Name: Zero Capacity Room
@@ -31098,7 +31166,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Under Maximum capacity: 'Enter a whole number, at least 1.'
 The venue is not created.
@@ -31112,7 +31180,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -31144,7 +31212,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Under Maximum capacity: 'Enter a whole number, at least 1.'
 The venue is not created.
@@ -31213,7 +31281,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Under Maximum capacity: 'Enter a whole number, at least 1.'
 The venue is not created.
@@ -32279,7 +32347,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>SPM-39-TC07</t>
         </is>
@@ -32291,7 +32359,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Venue 'Test Meeting Room' (TEST-01) exists with no layouts.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
@@ -32304,7 +32372,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>1. Open 'Test Meeting Room' from the Venues list
 2. Click 'Add a layout'
@@ -32322,7 +32390,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Layout 1 — Boardroom, Seats: 20
 Layout 2 — U-shape, Seats: 14</t>
@@ -32335,7 +32403,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>On reopening, both rows are shown: Boardroom with 20 seats and U-shape with 14 seats, each keeping its own value.
 The Venues list shows Layouts as '2 (max 20 seated)' for this venue.</t>
@@ -32348,7 +32416,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -32380,7 +32448,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>On reopening, both rows are shown: Boardroom with 20 seats and U-shape with 14 seats, each keeping its own value.
 The Venues list shows Layouts as '2 (max 20 seated)' for this venue.</t>
@@ -32448,7 +32516,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>On reopening, both rows are shown: Boardroom with 20 seats and U-shape with 14 seats, each keeping its own value.
 The Venues list shows Layouts as '2 (max 20 seated)' for this venue.</t>
